--- a/data/derived_data/3_CommunityComposition/Dataset_1/ps_rare_ITS_D1bis_tax_table.xlsx
+++ b/data/derived_data/3_CommunityComposition/Dataset_1/ps_rare_ITS_D1bis_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -83,16 +83,13 @@
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_105</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_111</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_113</t>
+    <t xml:space="preserve">pulcherrima</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_116</t>
@@ -239,9 +236,6 @@
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_58</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_59</t>
   </si>
   <si>
@@ -254,9 +248,6 @@
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_72</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
@@ -269,22 +260,13 @@
     <t xml:space="preserve">Cluster_87</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_87</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_89</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown_89</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknown_95</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_96</t>
@@ -699,22 +681,22 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -722,7 +704,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -748,59 +730,59 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
         <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -821,38 +803,38 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -873,12 +855,12 @@
         <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -899,12 +881,12 @@
         <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -930,25 +912,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -956,7 +938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -982,7 +964,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -1003,30 +985,30 @@
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>45</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>46</v>
-      </c>
-      <c r="G16" t="s">
-        <v>47</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1034,7 +1016,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1060,7 +1042,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1086,7 +1068,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1112,7 +1094,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1133,12 +1115,12 @@
         <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1159,38 +1141,38 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
         <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -1211,12 +1193,12 @@
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -1237,12 +1219,12 @@
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -1263,12 +1245,12 @@
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -1289,12 +1271,12 @@
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -1315,30 +1297,30 @@
         <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>62</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>63</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>64</v>
-      </c>
-      <c r="G28" t="s">
-        <v>65</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -1346,7 +1328,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -1367,30 +1349,30 @@
         <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>68</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>69</v>
-      </c>
-      <c r="G30" t="s">
-        <v>70</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -1398,7 +1380,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -1419,12 +1401,12 @@
         <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -1445,12 +1427,12 @@
         <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -1476,25 +1458,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -1502,7 +1484,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -1523,12 +1505,12 @@
         <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -1549,12 +1531,12 @@
         <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -1563,16 +1545,16 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
         <v>37</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>39</v>
-      </c>
-      <c r="G37" t="s">
-        <v>40</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -1580,25 +1562,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -1606,7 +1588,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -1627,12 +1609,12 @@
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -1653,12 +1635,12 @@
         <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1679,30 +1661,30 @@
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -1710,25 +1692,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -1736,7 +1718,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -1757,38 +1739,38 @@
         <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -1809,7 +1791,7 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
